--- a/Excel/EquipMakeConfig.xlsx
+++ b/Excel/EquipMakeConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CD3D4E-6DBD-43A6-9CC5-5B9ECA820C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBAB957-211B-48F2-8DC5-1A07593BA0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3251,19 +3251,19 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>10020001;20@10022010;20@10022008;4@10022009;2@10000131;10</t>
-  </si>
-  <si>
-    <t>10020001;30@10023010;30@10023008;4@10023009;2@10000131;15@10000143;3</t>
-  </si>
-  <si>
-    <t>10020001;40@10024010;40@10024008;4@10024009;2@10000131;20@10000143;5</t>
-  </si>
-  <si>
-    <t>10020001;50@10025010;50@10025008;4@10025009;2@10000131;25@10000143;10</t>
-  </si>
-  <si>
-    <t>10020001;100@10025010;100@10025008;6@10025009;3@10000131;30@10000143;20</t>
+    <t>10020001;20@10022010;20@10022008;4@10022009;2@10000166;10</t>
+  </si>
+  <si>
+    <t>10020001;30@10023010;30@10023008;4@10023009;2@10000166;15@10000143;3</t>
+  </si>
+  <si>
+    <t>10020001;40@10024010;40@10024008;4@10024009;2@10000166;20@10000143;5</t>
+  </si>
+  <si>
+    <t>10020001;50@10025010;50@10025008;4@10025009;2@10000166;25@10000143;10</t>
+  </si>
+  <si>
+    <t>10020001;100@10025010;100@10025008;6@10025009;3@10000166;30@10000143;20</t>
   </si>
 </sst>
 </file>
@@ -3641,7 +3641,7 @@
     <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/Excel/EquipMakeConfig.xlsx
+++ b/Excel/EquipMakeConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88857818-A6FF-4A8D-BBDE-B4774FAADB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1502CA66-DD7C-4C66-AD64-B6F1319C34BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipMakeProto" sheetId="1" r:id="rId1"/>
@@ -477,7 +477,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="901">
   <si>
     <t>#</t>
   </si>
@@ -3169,6 +3169,84 @@
   </si>
   <si>
     <t>10033008;1@10033008;1@10033010;1</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15801001;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15801002;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15801003;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15802001;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15802002;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15802003;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15803001;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15803002;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15803003;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15804001;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15804002;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15804003;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15805001;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15805002;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;30@15805003;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;40@10000182;40@15806001;1@10010085;10000@10000152;75@10000143;75</t>
+  </si>
+  <si>
+    <t>10000165;40@10000182;40@15807001;1@10010085;10000@10000152;75@10000143;75</t>
+  </si>
+  <si>
+    <t>10000165;40@10000182;40@15808001;1@10010085;10000@10000152;75@10000143;75</t>
+  </si>
+  <si>
+    <t>10000165;40@10000182;40@15809001;1@10010085;10000@10000152;75@10000143;75</t>
+  </si>
+  <si>
+    <t>10000165;80@10000182;80@15810001;1@10010085;10000@10000152;150@10000143;150</t>
+  </si>
+  <si>
+    <t>10000165;80@10000182;80@15810002;1@10010085;10000@10000152;150@10000143;150</t>
+  </si>
+  <si>
+    <t>10000165;80@10000182;80@15810101;1@10010085;10000@10000152;150@10000143;150</t>
+  </si>
+  <si>
+    <t>10000165;80@10000182;80@15810102;1@10010085;10000@10000152;150@10000143;150</t>
+  </si>
+  <si>
+    <t>10000165;60@10000182;60@15811001;1@10010085;10000@10000152;100@10000143;100</t>
+  </si>
+  <si>
+    <t>10000165;60@10000182;60@15811002;1@10010085;10000@10000152;100@10000143;100</t>
+  </si>
+  <si>
+    <t>10000165;60@10000182;60@15811003;1@10010085;10000@10000152;100@10000143;100</t>
   </si>
 </sst>
 </file>
@@ -3418,7 +3496,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3547,6 +3625,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -32410,2002 +32497,2002 @@
         <v>634</v>
       </c>
     </row>
-    <row r="386" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C386" s="6">
+    <row r="386" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C386" s="48">
         <v>5004001</v>
       </c>
-      <c r="D386" s="15" t="s">
+      <c r="D386" s="29" t="s">
         <v>541</v>
       </c>
-      <c r="E386" s="6">
-        <v>0</v>
-      </c>
-      <c r="F386" s="15">
+      <c r="E386" s="48">
+        <v>0</v>
+      </c>
+      <c r="F386" s="29">
         <v>15901001</v>
       </c>
-      <c r="G386" s="14">
-        <v>0</v>
-      </c>
-      <c r="H386" s="15">
+      <c r="G386" s="35">
+        <v>0</v>
+      </c>
+      <c r="H386" s="29">
         <v>60</v>
       </c>
-      <c r="I386" s="6">
-        <v>0</v>
-      </c>
-      <c r="J386" s="6">
-        <v>0</v>
-      </c>
-      <c r="K386" s="6">
-        <v>0</v>
-      </c>
-      <c r="L386" s="6">
-        <v>1</v>
-      </c>
-      <c r="M386" s="6">
-        <v>1</v>
-      </c>
-      <c r="N386" s="6">
-        <v>0</v>
-      </c>
-      <c r="O386" s="6">
-        <v>1</v>
-      </c>
-      <c r="P386" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q386" s="6">
-        <v>1</v>
-      </c>
-      <c r="R386" s="6">
-        <v>1</v>
-      </c>
-      <c r="S386" s="6">
-        <v>0</v>
-      </c>
-      <c r="T386" s="6">
-        <v>0</v>
-      </c>
-      <c r="U386" s="6">
-        <v>0</v>
-      </c>
-      <c r="V386" s="6">
-        <v>0</v>
-      </c>
-      <c r="W386" s="6">
-        <v>1</v>
-      </c>
-      <c r="X386" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y386" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z386" s="40" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="387" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C387" s="6">
+      <c r="I386" s="48">
+        <v>0</v>
+      </c>
+      <c r="J386" s="48">
+        <v>0</v>
+      </c>
+      <c r="K386" s="48">
+        <v>0</v>
+      </c>
+      <c r="L386" s="48">
+        <v>1</v>
+      </c>
+      <c r="M386" s="48">
+        <v>1</v>
+      </c>
+      <c r="N386" s="48">
+        <v>0</v>
+      </c>
+      <c r="O386" s="48">
+        <v>1</v>
+      </c>
+      <c r="P386" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q386" s="48">
+        <v>1</v>
+      </c>
+      <c r="R386" s="48">
+        <v>1</v>
+      </c>
+      <c r="S386" s="48">
+        <v>0</v>
+      </c>
+      <c r="T386" s="48">
+        <v>0</v>
+      </c>
+      <c r="U386" s="48">
+        <v>0</v>
+      </c>
+      <c r="V386" s="48">
+        <v>0</v>
+      </c>
+      <c r="W386" s="48">
+        <v>1</v>
+      </c>
+      <c r="X386" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y386" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z386" s="50" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="387" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C387" s="48">
         <v>5004002</v>
       </c>
-      <c r="D387" s="15" t="s">
+      <c r="D387" s="29" t="s">
         <v>543</v>
       </c>
-      <c r="E387" s="6">
-        <v>0</v>
-      </c>
-      <c r="F387" s="15">
+      <c r="E387" s="48">
+        <v>0</v>
+      </c>
+      <c r="F387" s="29">
         <v>15901002</v>
       </c>
-      <c r="G387" s="14">
-        <v>0</v>
-      </c>
-      <c r="H387" s="15">
+      <c r="G387" s="35">
+        <v>0</v>
+      </c>
+      <c r="H387" s="29">
         <v>60</v>
       </c>
-      <c r="I387" s="6">
-        <v>0</v>
-      </c>
-      <c r="J387" s="6">
-        <v>0</v>
-      </c>
-      <c r="K387" s="6">
-        <v>0</v>
-      </c>
-      <c r="L387" s="6">
-        <v>1</v>
-      </c>
-      <c r="M387" s="6">
-        <v>1</v>
-      </c>
-      <c r="N387" s="6">
-        <v>0</v>
-      </c>
-      <c r="O387" s="6">
-        <v>1</v>
-      </c>
-      <c r="P387" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q387" s="6">
-        <v>1</v>
-      </c>
-      <c r="R387" s="6">
-        <v>1</v>
-      </c>
-      <c r="S387" s="6">
-        <v>0</v>
-      </c>
-      <c r="T387" s="6">
-        <v>0</v>
-      </c>
-      <c r="U387" s="6">
-        <v>0</v>
-      </c>
-      <c r="V387" s="6">
-        <v>0</v>
-      </c>
-      <c r="W387" s="6">
-        <v>1</v>
-      </c>
-      <c r="X387" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y387" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z387" s="40" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="388" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C388" s="6">
+      <c r="I387" s="48">
+        <v>0</v>
+      </c>
+      <c r="J387" s="48">
+        <v>0</v>
+      </c>
+      <c r="K387" s="48">
+        <v>0</v>
+      </c>
+      <c r="L387" s="48">
+        <v>1</v>
+      </c>
+      <c r="M387" s="48">
+        <v>1</v>
+      </c>
+      <c r="N387" s="48">
+        <v>0</v>
+      </c>
+      <c r="O387" s="48">
+        <v>1</v>
+      </c>
+      <c r="P387" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q387" s="48">
+        <v>1</v>
+      </c>
+      <c r="R387" s="48">
+        <v>1</v>
+      </c>
+      <c r="S387" s="48">
+        <v>0</v>
+      </c>
+      <c r="T387" s="48">
+        <v>0</v>
+      </c>
+      <c r="U387" s="48">
+        <v>0</v>
+      </c>
+      <c r="V387" s="48">
+        <v>0</v>
+      </c>
+      <c r="W387" s="48">
+        <v>1</v>
+      </c>
+      <c r="X387" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y387" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z387" s="50" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="388" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C388" s="48">
         <v>5004003</v>
       </c>
-      <c r="D388" s="15" t="s">
+      <c r="D388" s="29" t="s">
         <v>544</v>
       </c>
-      <c r="E388" s="6">
-        <v>0</v>
-      </c>
-      <c r="F388" s="15">
+      <c r="E388" s="48">
+        <v>0</v>
+      </c>
+      <c r="F388" s="29">
         <v>15901003</v>
       </c>
-      <c r="G388" s="14">
-        <v>0</v>
-      </c>
-      <c r="H388" s="15">
+      <c r="G388" s="35">
+        <v>0</v>
+      </c>
+      <c r="H388" s="29">
         <v>60</v>
       </c>
-      <c r="I388" s="6">
-        <v>0</v>
-      </c>
-      <c r="J388" s="6">
-        <v>0</v>
-      </c>
-      <c r="K388" s="6">
-        <v>0</v>
-      </c>
-      <c r="L388" s="6">
-        <v>1</v>
-      </c>
-      <c r="M388" s="6">
-        <v>1</v>
-      </c>
-      <c r="N388" s="6">
-        <v>0</v>
-      </c>
-      <c r="O388" s="6">
-        <v>1</v>
-      </c>
-      <c r="P388" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q388" s="6">
-        <v>1</v>
-      </c>
-      <c r="R388" s="6">
-        <v>1</v>
-      </c>
-      <c r="S388" s="6">
-        <v>0</v>
-      </c>
-      <c r="T388" s="6">
-        <v>0</v>
-      </c>
-      <c r="U388" s="6">
-        <v>0</v>
-      </c>
-      <c r="V388" s="6">
-        <v>0</v>
-      </c>
-      <c r="W388" s="6">
-        <v>1</v>
-      </c>
-      <c r="X388" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y388" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z388" s="40" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="389" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C389" s="6">
+      <c r="I388" s="48">
+        <v>0</v>
+      </c>
+      <c r="J388" s="48">
+        <v>0</v>
+      </c>
+      <c r="K388" s="48">
+        <v>0</v>
+      </c>
+      <c r="L388" s="48">
+        <v>1</v>
+      </c>
+      <c r="M388" s="48">
+        <v>1</v>
+      </c>
+      <c r="N388" s="48">
+        <v>0</v>
+      </c>
+      <c r="O388" s="48">
+        <v>1</v>
+      </c>
+      <c r="P388" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q388" s="48">
+        <v>1</v>
+      </c>
+      <c r="R388" s="48">
+        <v>1</v>
+      </c>
+      <c r="S388" s="48">
+        <v>0</v>
+      </c>
+      <c r="T388" s="48">
+        <v>0</v>
+      </c>
+      <c r="U388" s="48">
+        <v>0</v>
+      </c>
+      <c r="V388" s="48">
+        <v>0</v>
+      </c>
+      <c r="W388" s="48">
+        <v>1</v>
+      </c>
+      <c r="X388" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y388" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z388" s="50" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="389" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C389" s="48">
         <v>5004011</v>
       </c>
-      <c r="D389" s="15" t="s">
+      <c r="D389" s="29" t="s">
         <v>545</v>
       </c>
-      <c r="E389" s="6">
-        <v>0</v>
-      </c>
-      <c r="F389" s="15">
+      <c r="E389" s="48">
+        <v>0</v>
+      </c>
+      <c r="F389" s="29">
         <v>15902001</v>
       </c>
-      <c r="G389" s="14">
-        <v>0</v>
-      </c>
-      <c r="H389" s="15">
+      <c r="G389" s="35">
+        <v>0</v>
+      </c>
+      <c r="H389" s="29">
         <v>60</v>
       </c>
-      <c r="I389" s="6">
-        <v>0</v>
-      </c>
-      <c r="J389" s="6">
-        <v>0</v>
-      </c>
-      <c r="K389" s="6">
-        <v>0</v>
-      </c>
-      <c r="L389" s="6">
-        <v>1</v>
-      </c>
-      <c r="M389" s="6">
-        <v>1</v>
-      </c>
-      <c r="N389" s="6">
-        <v>0</v>
-      </c>
-      <c r="O389" s="6">
-        <v>1</v>
-      </c>
-      <c r="P389" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q389" s="6">
-        <v>1</v>
-      </c>
-      <c r="R389" s="6">
-        <v>1</v>
-      </c>
-      <c r="S389" s="6">
-        <v>0</v>
-      </c>
-      <c r="T389" s="6">
-        <v>0</v>
-      </c>
-      <c r="U389" s="6">
-        <v>0</v>
-      </c>
-      <c r="V389" s="6">
-        <v>0</v>
-      </c>
-      <c r="W389" s="6">
-        <v>1</v>
-      </c>
-      <c r="X389" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y389" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z389" s="40" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="390" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C390" s="6">
+      <c r="I389" s="48">
+        <v>0</v>
+      </c>
+      <c r="J389" s="48">
+        <v>0</v>
+      </c>
+      <c r="K389" s="48">
+        <v>0</v>
+      </c>
+      <c r="L389" s="48">
+        <v>1</v>
+      </c>
+      <c r="M389" s="48">
+        <v>1</v>
+      </c>
+      <c r="N389" s="48">
+        <v>0</v>
+      </c>
+      <c r="O389" s="48">
+        <v>1</v>
+      </c>
+      <c r="P389" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q389" s="48">
+        <v>1</v>
+      </c>
+      <c r="R389" s="48">
+        <v>1</v>
+      </c>
+      <c r="S389" s="48">
+        <v>0</v>
+      </c>
+      <c r="T389" s="48">
+        <v>0</v>
+      </c>
+      <c r="U389" s="48">
+        <v>0</v>
+      </c>
+      <c r="V389" s="48">
+        <v>0</v>
+      </c>
+      <c r="W389" s="48">
+        <v>1</v>
+      </c>
+      <c r="X389" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y389" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z389" s="50" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="390" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C390" s="48">
         <v>5004012</v>
       </c>
-      <c r="D390" s="15" t="s">
+      <c r="D390" s="29" t="s">
         <v>546</v>
       </c>
-      <c r="E390" s="6">
-        <v>0</v>
-      </c>
-      <c r="F390" s="15">
+      <c r="E390" s="48">
+        <v>0</v>
+      </c>
+      <c r="F390" s="29">
         <v>15902002</v>
       </c>
-      <c r="G390" s="14">
-        <v>0</v>
-      </c>
-      <c r="H390" s="15">
+      <c r="G390" s="35">
+        <v>0</v>
+      </c>
+      <c r="H390" s="29">
         <v>60</v>
       </c>
-      <c r="I390" s="6">
-        <v>0</v>
-      </c>
-      <c r="J390" s="6">
-        <v>0</v>
-      </c>
-      <c r="K390" s="6">
-        <v>0</v>
-      </c>
-      <c r="L390" s="6">
-        <v>1</v>
-      </c>
-      <c r="M390" s="6">
-        <v>1</v>
-      </c>
-      <c r="N390" s="6">
-        <v>0</v>
-      </c>
-      <c r="O390" s="6">
-        <v>1</v>
-      </c>
-      <c r="P390" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q390" s="6">
-        <v>1</v>
-      </c>
-      <c r="R390" s="6">
-        <v>1</v>
-      </c>
-      <c r="S390" s="6">
-        <v>0</v>
-      </c>
-      <c r="T390" s="6">
-        <v>0</v>
-      </c>
-      <c r="U390" s="6">
-        <v>0</v>
-      </c>
-      <c r="V390" s="6">
-        <v>0</v>
-      </c>
-      <c r="W390" s="6">
-        <v>1</v>
-      </c>
-      <c r="X390" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y390" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z390" s="40" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="391" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C391" s="6">
+      <c r="I390" s="48">
+        <v>0</v>
+      </c>
+      <c r="J390" s="48">
+        <v>0</v>
+      </c>
+      <c r="K390" s="48">
+        <v>0</v>
+      </c>
+      <c r="L390" s="48">
+        <v>1</v>
+      </c>
+      <c r="M390" s="48">
+        <v>1</v>
+      </c>
+      <c r="N390" s="48">
+        <v>0</v>
+      </c>
+      <c r="O390" s="48">
+        <v>1</v>
+      </c>
+      <c r="P390" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q390" s="48">
+        <v>1</v>
+      </c>
+      <c r="R390" s="48">
+        <v>1</v>
+      </c>
+      <c r="S390" s="48">
+        <v>0</v>
+      </c>
+      <c r="T390" s="48">
+        <v>0</v>
+      </c>
+      <c r="U390" s="48">
+        <v>0</v>
+      </c>
+      <c r="V390" s="48">
+        <v>0</v>
+      </c>
+      <c r="W390" s="48">
+        <v>1</v>
+      </c>
+      <c r="X390" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y390" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z390" s="50" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="391" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C391" s="48">
         <v>5004013</v>
       </c>
-      <c r="D391" s="15" t="s">
+      <c r="D391" s="29" t="s">
         <v>547</v>
       </c>
-      <c r="E391" s="6">
-        <v>0</v>
-      </c>
-      <c r="F391" s="15">
+      <c r="E391" s="48">
+        <v>0</v>
+      </c>
+      <c r="F391" s="29">
         <v>15902003</v>
       </c>
-      <c r="G391" s="14">
-        <v>0</v>
-      </c>
-      <c r="H391" s="15">
+      <c r="G391" s="35">
+        <v>0</v>
+      </c>
+      <c r="H391" s="29">
         <v>60</v>
       </c>
-      <c r="I391" s="6">
-        <v>0</v>
-      </c>
-      <c r="J391" s="6">
-        <v>0</v>
-      </c>
-      <c r="K391" s="6">
-        <v>0</v>
-      </c>
-      <c r="L391" s="6">
-        <v>1</v>
-      </c>
-      <c r="M391" s="6">
-        <v>1</v>
-      </c>
-      <c r="N391" s="6">
-        <v>0</v>
-      </c>
-      <c r="O391" s="6">
-        <v>1</v>
-      </c>
-      <c r="P391" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q391" s="6">
-        <v>1</v>
-      </c>
-      <c r="R391" s="6">
-        <v>1</v>
-      </c>
-      <c r="S391" s="6">
-        <v>0</v>
-      </c>
-      <c r="T391" s="6">
-        <v>0</v>
-      </c>
-      <c r="U391" s="6">
-        <v>0</v>
-      </c>
-      <c r="V391" s="6">
-        <v>0</v>
-      </c>
-      <c r="W391" s="6">
-        <v>1</v>
-      </c>
-      <c r="X391" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y391" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z391" s="40" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="392" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C392" s="6">
+      <c r="I391" s="48">
+        <v>0</v>
+      </c>
+      <c r="J391" s="48">
+        <v>0</v>
+      </c>
+      <c r="K391" s="48">
+        <v>0</v>
+      </c>
+      <c r="L391" s="48">
+        <v>1</v>
+      </c>
+      <c r="M391" s="48">
+        <v>1</v>
+      </c>
+      <c r="N391" s="48">
+        <v>0</v>
+      </c>
+      <c r="O391" s="48">
+        <v>1</v>
+      </c>
+      <c r="P391" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q391" s="48">
+        <v>1</v>
+      </c>
+      <c r="R391" s="48">
+        <v>1</v>
+      </c>
+      <c r="S391" s="48">
+        <v>0</v>
+      </c>
+      <c r="T391" s="48">
+        <v>0</v>
+      </c>
+      <c r="U391" s="48">
+        <v>0</v>
+      </c>
+      <c r="V391" s="48">
+        <v>0</v>
+      </c>
+      <c r="W391" s="48">
+        <v>1</v>
+      </c>
+      <c r="X391" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y391" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z391" s="50" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="392" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C392" s="48">
         <v>5004021</v>
       </c>
-      <c r="D392" s="15" t="s">
+      <c r="D392" s="29" t="s">
         <v>548</v>
       </c>
-      <c r="E392" s="6">
-        <v>0</v>
-      </c>
-      <c r="F392" s="15">
+      <c r="E392" s="48">
+        <v>0</v>
+      </c>
+      <c r="F392" s="29">
         <v>15903001</v>
       </c>
-      <c r="G392" s="14">
-        <v>0</v>
-      </c>
-      <c r="H392" s="15">
+      <c r="G392" s="35">
+        <v>0</v>
+      </c>
+      <c r="H392" s="29">
         <v>60</v>
       </c>
-      <c r="I392" s="6">
-        <v>0</v>
-      </c>
-      <c r="J392" s="6">
-        <v>0</v>
-      </c>
-      <c r="K392" s="6">
-        <v>0</v>
-      </c>
-      <c r="L392" s="6">
-        <v>1</v>
-      </c>
-      <c r="M392" s="6">
-        <v>1</v>
-      </c>
-      <c r="N392" s="6">
-        <v>0</v>
-      </c>
-      <c r="O392" s="6">
-        <v>1</v>
-      </c>
-      <c r="P392" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q392" s="6">
-        <v>1</v>
-      </c>
-      <c r="R392" s="6">
-        <v>1</v>
-      </c>
-      <c r="S392" s="6">
-        <v>0</v>
-      </c>
-      <c r="T392" s="6">
-        <v>0</v>
-      </c>
-      <c r="U392" s="6">
-        <v>0</v>
-      </c>
-      <c r="V392" s="6">
-        <v>0</v>
-      </c>
-      <c r="W392" s="6">
-        <v>1</v>
-      </c>
-      <c r="X392" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y392" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z392" s="40" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="393" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C393" s="6">
+      <c r="I392" s="48">
+        <v>0</v>
+      </c>
+      <c r="J392" s="48">
+        <v>0</v>
+      </c>
+      <c r="K392" s="48">
+        <v>0</v>
+      </c>
+      <c r="L392" s="48">
+        <v>1</v>
+      </c>
+      <c r="M392" s="48">
+        <v>1</v>
+      </c>
+      <c r="N392" s="48">
+        <v>0</v>
+      </c>
+      <c r="O392" s="48">
+        <v>1</v>
+      </c>
+      <c r="P392" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q392" s="48">
+        <v>1</v>
+      </c>
+      <c r="R392" s="48">
+        <v>1</v>
+      </c>
+      <c r="S392" s="48">
+        <v>0</v>
+      </c>
+      <c r="T392" s="48">
+        <v>0</v>
+      </c>
+      <c r="U392" s="48">
+        <v>0</v>
+      </c>
+      <c r="V392" s="48">
+        <v>0</v>
+      </c>
+      <c r="W392" s="48">
+        <v>1</v>
+      </c>
+      <c r="X392" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y392" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z392" s="50" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="393" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C393" s="48">
         <v>5004022</v>
       </c>
-      <c r="D393" s="15" t="s">
+      <c r="D393" s="29" t="s">
         <v>549</v>
       </c>
-      <c r="E393" s="6">
-        <v>0</v>
-      </c>
-      <c r="F393" s="15">
+      <c r="E393" s="48">
+        <v>0</v>
+      </c>
+      <c r="F393" s="29">
         <v>15903002</v>
       </c>
-      <c r="G393" s="14">
-        <v>0</v>
-      </c>
-      <c r="H393" s="15">
+      <c r="G393" s="35">
+        <v>0</v>
+      </c>
+      <c r="H393" s="29">
         <v>60</v>
       </c>
-      <c r="I393" s="6">
-        <v>0</v>
-      </c>
-      <c r="J393" s="6">
-        <v>0</v>
-      </c>
-      <c r="K393" s="6">
-        <v>0</v>
-      </c>
-      <c r="L393" s="6">
-        <v>1</v>
-      </c>
-      <c r="M393" s="6">
-        <v>1</v>
-      </c>
-      <c r="N393" s="6">
-        <v>0</v>
-      </c>
-      <c r="O393" s="6">
-        <v>1</v>
-      </c>
-      <c r="P393" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q393" s="6">
-        <v>1</v>
-      </c>
-      <c r="R393" s="6">
-        <v>1</v>
-      </c>
-      <c r="S393" s="6">
-        <v>0</v>
-      </c>
-      <c r="T393" s="6">
-        <v>0</v>
-      </c>
-      <c r="U393" s="6">
-        <v>0</v>
-      </c>
-      <c r="V393" s="6">
-        <v>0</v>
-      </c>
-      <c r="W393" s="6">
-        <v>1</v>
-      </c>
-      <c r="X393" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y393" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z393" s="40" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="394" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C394" s="6">
+      <c r="I393" s="48">
+        <v>0</v>
+      </c>
+      <c r="J393" s="48">
+        <v>0</v>
+      </c>
+      <c r="K393" s="48">
+        <v>0</v>
+      </c>
+      <c r="L393" s="48">
+        <v>1</v>
+      </c>
+      <c r="M393" s="48">
+        <v>1</v>
+      </c>
+      <c r="N393" s="48">
+        <v>0</v>
+      </c>
+      <c r="O393" s="48">
+        <v>1</v>
+      </c>
+      <c r="P393" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q393" s="48">
+        <v>1</v>
+      </c>
+      <c r="R393" s="48">
+        <v>1</v>
+      </c>
+      <c r="S393" s="48">
+        <v>0</v>
+      </c>
+      <c r="T393" s="48">
+        <v>0</v>
+      </c>
+      <c r="U393" s="48">
+        <v>0</v>
+      </c>
+      <c r="V393" s="48">
+        <v>0</v>
+      </c>
+      <c r="W393" s="48">
+        <v>1</v>
+      </c>
+      <c r="X393" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y393" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z393" s="50" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="394" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C394" s="48">
         <v>5004023</v>
       </c>
-      <c r="D394" s="15" t="s">
+      <c r="D394" s="29" t="s">
         <v>550</v>
       </c>
-      <c r="E394" s="6">
-        <v>0</v>
-      </c>
-      <c r="F394" s="15">
+      <c r="E394" s="48">
+        <v>0</v>
+      </c>
+      <c r="F394" s="29">
         <v>15903003</v>
       </c>
-      <c r="G394" s="14">
-        <v>0</v>
-      </c>
-      <c r="H394" s="15">
+      <c r="G394" s="35">
+        <v>0</v>
+      </c>
+      <c r="H394" s="29">
         <v>60</v>
       </c>
-      <c r="I394" s="6">
-        <v>0</v>
-      </c>
-      <c r="J394" s="6">
-        <v>0</v>
-      </c>
-      <c r="K394" s="6">
-        <v>0</v>
-      </c>
-      <c r="L394" s="6">
-        <v>1</v>
-      </c>
-      <c r="M394" s="6">
-        <v>1</v>
-      </c>
-      <c r="N394" s="6">
-        <v>0</v>
-      </c>
-      <c r="O394" s="6">
-        <v>1</v>
-      </c>
-      <c r="P394" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q394" s="6">
-        <v>1</v>
-      </c>
-      <c r="R394" s="6">
-        <v>1</v>
-      </c>
-      <c r="S394" s="6">
-        <v>0</v>
-      </c>
-      <c r="T394" s="6">
-        <v>0</v>
-      </c>
-      <c r="U394" s="6">
-        <v>0</v>
-      </c>
-      <c r="V394" s="6">
-        <v>0</v>
-      </c>
-      <c r="W394" s="6">
-        <v>1</v>
-      </c>
-      <c r="X394" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y394" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z394" s="40" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="395" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C395" s="6">
+      <c r="I394" s="48">
+        <v>0</v>
+      </c>
+      <c r="J394" s="48">
+        <v>0</v>
+      </c>
+      <c r="K394" s="48">
+        <v>0</v>
+      </c>
+      <c r="L394" s="48">
+        <v>1</v>
+      </c>
+      <c r="M394" s="48">
+        <v>1</v>
+      </c>
+      <c r="N394" s="48">
+        <v>0</v>
+      </c>
+      <c r="O394" s="48">
+        <v>1</v>
+      </c>
+      <c r="P394" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q394" s="48">
+        <v>1</v>
+      </c>
+      <c r="R394" s="48">
+        <v>1</v>
+      </c>
+      <c r="S394" s="48">
+        <v>0</v>
+      </c>
+      <c r="T394" s="48">
+        <v>0</v>
+      </c>
+      <c r="U394" s="48">
+        <v>0</v>
+      </c>
+      <c r="V394" s="48">
+        <v>0</v>
+      </c>
+      <c r="W394" s="48">
+        <v>1</v>
+      </c>
+      <c r="X394" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y394" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z394" s="50" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="395" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C395" s="48">
         <v>5004031</v>
       </c>
-      <c r="D395" s="15" t="s">
+      <c r="D395" s="29" t="s">
         <v>551</v>
       </c>
-      <c r="E395" s="6">
-        <v>0</v>
-      </c>
-      <c r="F395" s="15">
+      <c r="E395" s="48">
+        <v>0</v>
+      </c>
+      <c r="F395" s="29">
         <v>15904001</v>
       </c>
-      <c r="G395" s="14">
-        <v>0</v>
-      </c>
-      <c r="H395" s="15">
+      <c r="G395" s="35">
+        <v>0</v>
+      </c>
+      <c r="H395" s="29">
         <v>60</v>
       </c>
-      <c r="I395" s="6">
-        <v>0</v>
-      </c>
-      <c r="J395" s="6">
-        <v>0</v>
-      </c>
-      <c r="K395" s="6">
-        <v>0</v>
-      </c>
-      <c r="L395" s="6">
-        <v>1</v>
-      </c>
-      <c r="M395" s="6">
-        <v>1</v>
-      </c>
-      <c r="N395" s="6">
-        <v>0</v>
-      </c>
-      <c r="O395" s="6">
-        <v>1</v>
-      </c>
-      <c r="P395" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q395" s="6">
-        <v>1</v>
-      </c>
-      <c r="R395" s="6">
-        <v>1</v>
-      </c>
-      <c r="S395" s="6">
-        <v>0</v>
-      </c>
-      <c r="T395" s="6">
-        <v>0</v>
-      </c>
-      <c r="U395" s="6">
-        <v>0</v>
-      </c>
-      <c r="V395" s="6">
-        <v>0</v>
-      </c>
-      <c r="W395" s="6">
-        <v>1</v>
-      </c>
-      <c r="X395" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y395" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z395" s="40" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="396" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C396" s="6">
+      <c r="I395" s="48">
+        <v>0</v>
+      </c>
+      <c r="J395" s="48">
+        <v>0</v>
+      </c>
+      <c r="K395" s="48">
+        <v>0</v>
+      </c>
+      <c r="L395" s="48">
+        <v>1</v>
+      </c>
+      <c r="M395" s="48">
+        <v>1</v>
+      </c>
+      <c r="N395" s="48">
+        <v>0</v>
+      </c>
+      <c r="O395" s="48">
+        <v>1</v>
+      </c>
+      <c r="P395" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q395" s="48">
+        <v>1</v>
+      </c>
+      <c r="R395" s="48">
+        <v>1</v>
+      </c>
+      <c r="S395" s="48">
+        <v>0</v>
+      </c>
+      <c r="T395" s="48">
+        <v>0</v>
+      </c>
+      <c r="U395" s="48">
+        <v>0</v>
+      </c>
+      <c r="V395" s="48">
+        <v>0</v>
+      </c>
+      <c r="W395" s="48">
+        <v>1</v>
+      </c>
+      <c r="X395" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y395" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z395" s="50" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="396" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C396" s="48">
         <v>5004032</v>
       </c>
-      <c r="D396" s="15" t="s">
+      <c r="D396" s="29" t="s">
         <v>552</v>
       </c>
-      <c r="E396" s="6">
-        <v>0</v>
-      </c>
-      <c r="F396" s="15">
+      <c r="E396" s="48">
+        <v>0</v>
+      </c>
+      <c r="F396" s="29">
         <v>15904002</v>
       </c>
-      <c r="G396" s="14">
-        <v>0</v>
-      </c>
-      <c r="H396" s="15">
+      <c r="G396" s="35">
+        <v>0</v>
+      </c>
+      <c r="H396" s="29">
         <v>60</v>
       </c>
-      <c r="I396" s="6">
-        <v>0</v>
-      </c>
-      <c r="J396" s="6">
-        <v>0</v>
-      </c>
-      <c r="K396" s="6">
-        <v>0</v>
-      </c>
-      <c r="L396" s="6">
-        <v>1</v>
-      </c>
-      <c r="M396" s="6">
-        <v>1</v>
-      </c>
-      <c r="N396" s="6">
-        <v>0</v>
-      </c>
-      <c r="O396" s="6">
-        <v>1</v>
-      </c>
-      <c r="P396" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q396" s="6">
-        <v>1</v>
-      </c>
-      <c r="R396" s="6">
-        <v>1</v>
-      </c>
-      <c r="S396" s="6">
-        <v>0</v>
-      </c>
-      <c r="T396" s="6">
-        <v>0</v>
-      </c>
-      <c r="U396" s="6">
-        <v>0</v>
-      </c>
-      <c r="V396" s="6">
-        <v>0</v>
-      </c>
-      <c r="W396" s="6">
-        <v>1</v>
-      </c>
-      <c r="X396" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y396" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z396" s="40" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="397" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C397" s="6">
+      <c r="I396" s="48">
+        <v>0</v>
+      </c>
+      <c r="J396" s="48">
+        <v>0</v>
+      </c>
+      <c r="K396" s="48">
+        <v>0</v>
+      </c>
+      <c r="L396" s="48">
+        <v>1</v>
+      </c>
+      <c r="M396" s="48">
+        <v>1</v>
+      </c>
+      <c r="N396" s="48">
+        <v>0</v>
+      </c>
+      <c r="O396" s="48">
+        <v>1</v>
+      </c>
+      <c r="P396" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q396" s="48">
+        <v>1</v>
+      </c>
+      <c r="R396" s="48">
+        <v>1</v>
+      </c>
+      <c r="S396" s="48">
+        <v>0</v>
+      </c>
+      <c r="T396" s="48">
+        <v>0</v>
+      </c>
+      <c r="U396" s="48">
+        <v>0</v>
+      </c>
+      <c r="V396" s="48">
+        <v>0</v>
+      </c>
+      <c r="W396" s="48">
+        <v>1</v>
+      </c>
+      <c r="X396" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y396" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z396" s="50" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="397" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C397" s="48">
         <v>5004033</v>
       </c>
-      <c r="D397" s="15" t="s">
+      <c r="D397" s="29" t="s">
         <v>553</v>
       </c>
-      <c r="E397" s="6">
-        <v>0</v>
-      </c>
-      <c r="F397" s="15">
+      <c r="E397" s="48">
+        <v>0</v>
+      </c>
+      <c r="F397" s="29">
         <v>15904003</v>
       </c>
-      <c r="G397" s="14">
-        <v>0</v>
-      </c>
-      <c r="H397" s="15">
+      <c r="G397" s="35">
+        <v>0</v>
+      </c>
+      <c r="H397" s="29">
         <v>60</v>
       </c>
-      <c r="I397" s="6">
-        <v>0</v>
-      </c>
-      <c r="J397" s="6">
-        <v>0</v>
-      </c>
-      <c r="K397" s="6">
-        <v>0</v>
-      </c>
-      <c r="L397" s="6">
-        <v>1</v>
-      </c>
-      <c r="M397" s="6">
-        <v>1</v>
-      </c>
-      <c r="N397" s="6">
-        <v>0</v>
-      </c>
-      <c r="O397" s="6">
-        <v>1</v>
-      </c>
-      <c r="P397" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q397" s="6">
-        <v>1</v>
-      </c>
-      <c r="R397" s="6">
-        <v>1</v>
-      </c>
-      <c r="S397" s="6">
-        <v>0</v>
-      </c>
-      <c r="T397" s="6">
-        <v>0</v>
-      </c>
-      <c r="U397" s="6">
-        <v>0</v>
-      </c>
-      <c r="V397" s="6">
-        <v>0</v>
-      </c>
-      <c r="W397" s="6">
-        <v>1</v>
-      </c>
-      <c r="X397" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y397" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z397" s="40" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="398" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C398" s="6">
+      <c r="I397" s="48">
+        <v>0</v>
+      </c>
+      <c r="J397" s="48">
+        <v>0</v>
+      </c>
+      <c r="K397" s="48">
+        <v>0</v>
+      </c>
+      <c r="L397" s="48">
+        <v>1</v>
+      </c>
+      <c r="M397" s="48">
+        <v>1</v>
+      </c>
+      <c r="N397" s="48">
+        <v>0</v>
+      </c>
+      <c r="O397" s="48">
+        <v>1</v>
+      </c>
+      <c r="P397" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q397" s="48">
+        <v>1</v>
+      </c>
+      <c r="R397" s="48">
+        <v>1</v>
+      </c>
+      <c r="S397" s="48">
+        <v>0</v>
+      </c>
+      <c r="T397" s="48">
+        <v>0</v>
+      </c>
+      <c r="U397" s="48">
+        <v>0</v>
+      </c>
+      <c r="V397" s="48">
+        <v>0</v>
+      </c>
+      <c r="W397" s="48">
+        <v>1</v>
+      </c>
+      <c r="X397" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y397" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z397" s="50" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="398" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C398" s="48">
         <v>5004041</v>
       </c>
-      <c r="D398" s="15" t="s">
+      <c r="D398" s="29" t="s">
         <v>554</v>
       </c>
-      <c r="E398" s="6">
-        <v>0</v>
-      </c>
-      <c r="F398" s="15">
+      <c r="E398" s="48">
+        <v>0</v>
+      </c>
+      <c r="F398" s="29">
         <v>15905001</v>
       </c>
-      <c r="G398" s="14">
-        <v>0</v>
-      </c>
-      <c r="H398" s="15">
+      <c r="G398" s="35">
+        <v>0</v>
+      </c>
+      <c r="H398" s="29">
         <v>60</v>
       </c>
-      <c r="I398" s="6">
-        <v>0</v>
-      </c>
-      <c r="J398" s="6">
-        <v>0</v>
-      </c>
-      <c r="K398" s="6">
-        <v>0</v>
-      </c>
-      <c r="L398" s="6">
-        <v>1</v>
-      </c>
-      <c r="M398" s="6">
-        <v>1</v>
-      </c>
-      <c r="N398" s="6">
-        <v>0</v>
-      </c>
-      <c r="O398" s="6">
-        <v>1</v>
-      </c>
-      <c r="P398" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q398" s="6">
-        <v>1</v>
-      </c>
-      <c r="R398" s="6">
-        <v>1</v>
-      </c>
-      <c r="S398" s="6">
-        <v>0</v>
-      </c>
-      <c r="T398" s="6">
-        <v>0</v>
-      </c>
-      <c r="U398" s="6">
-        <v>0</v>
-      </c>
-      <c r="V398" s="6">
-        <v>0</v>
-      </c>
-      <c r="W398" s="6">
-        <v>1</v>
-      </c>
-      <c r="X398" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y398" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z398" s="40" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="399" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C399" s="6">
+      <c r="I398" s="48">
+        <v>0</v>
+      </c>
+      <c r="J398" s="48">
+        <v>0</v>
+      </c>
+      <c r="K398" s="48">
+        <v>0</v>
+      </c>
+      <c r="L398" s="48">
+        <v>1</v>
+      </c>
+      <c r="M398" s="48">
+        <v>1</v>
+      </c>
+      <c r="N398" s="48">
+        <v>0</v>
+      </c>
+      <c r="O398" s="48">
+        <v>1</v>
+      </c>
+      <c r="P398" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q398" s="48">
+        <v>1</v>
+      </c>
+      <c r="R398" s="48">
+        <v>1</v>
+      </c>
+      <c r="S398" s="48">
+        <v>0</v>
+      </c>
+      <c r="T398" s="48">
+        <v>0</v>
+      </c>
+      <c r="U398" s="48">
+        <v>0</v>
+      </c>
+      <c r="V398" s="48">
+        <v>0</v>
+      </c>
+      <c r="W398" s="48">
+        <v>1</v>
+      </c>
+      <c r="X398" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y398" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z398" s="50" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="399" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C399" s="48">
         <v>5004042</v>
       </c>
-      <c r="D399" s="15" t="s">
+      <c r="D399" s="29" t="s">
         <v>555</v>
       </c>
-      <c r="E399" s="6">
-        <v>0</v>
-      </c>
-      <c r="F399" s="15">
+      <c r="E399" s="48">
+        <v>0</v>
+      </c>
+      <c r="F399" s="29">
         <v>15905002</v>
       </c>
-      <c r="G399" s="14">
-        <v>0</v>
-      </c>
-      <c r="H399" s="15">
+      <c r="G399" s="35">
+        <v>0</v>
+      </c>
+      <c r="H399" s="29">
         <v>60</v>
       </c>
-      <c r="I399" s="6">
-        <v>0</v>
-      </c>
-      <c r="J399" s="6">
-        <v>0</v>
-      </c>
-      <c r="K399" s="6">
-        <v>0</v>
-      </c>
-      <c r="L399" s="6">
-        <v>1</v>
-      </c>
-      <c r="M399" s="6">
-        <v>1</v>
-      </c>
-      <c r="N399" s="6">
-        <v>0</v>
-      </c>
-      <c r="O399" s="6">
-        <v>1</v>
-      </c>
-      <c r="P399" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q399" s="6">
-        <v>1</v>
-      </c>
-      <c r="R399" s="6">
-        <v>1</v>
-      </c>
-      <c r="S399" s="6">
-        <v>0</v>
-      </c>
-      <c r="T399" s="6">
-        <v>0</v>
-      </c>
-      <c r="U399" s="6">
-        <v>0</v>
-      </c>
-      <c r="V399" s="6">
-        <v>0</v>
-      </c>
-      <c r="W399" s="6">
-        <v>1</v>
-      </c>
-      <c r="X399" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y399" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z399" s="40" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="400" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C400" s="6">
+      <c r="I399" s="48">
+        <v>0</v>
+      </c>
+      <c r="J399" s="48">
+        <v>0</v>
+      </c>
+      <c r="K399" s="48">
+        <v>0</v>
+      </c>
+      <c r="L399" s="48">
+        <v>1</v>
+      </c>
+      <c r="M399" s="48">
+        <v>1</v>
+      </c>
+      <c r="N399" s="48">
+        <v>0</v>
+      </c>
+      <c r="O399" s="48">
+        <v>1</v>
+      </c>
+      <c r="P399" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q399" s="48">
+        <v>1</v>
+      </c>
+      <c r="R399" s="48">
+        <v>1</v>
+      </c>
+      <c r="S399" s="48">
+        <v>0</v>
+      </c>
+      <c r="T399" s="48">
+        <v>0</v>
+      </c>
+      <c r="U399" s="48">
+        <v>0</v>
+      </c>
+      <c r="V399" s="48">
+        <v>0</v>
+      </c>
+      <c r="W399" s="48">
+        <v>1</v>
+      </c>
+      <c r="X399" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y399" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z399" s="50" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="400" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C400" s="48">
         <v>5004043</v>
       </c>
-      <c r="D400" s="15" t="s">
+      <c r="D400" s="29" t="s">
         <v>556</v>
       </c>
-      <c r="E400" s="6">
-        <v>0</v>
-      </c>
-      <c r="F400" s="15">
+      <c r="E400" s="48">
+        <v>0</v>
+      </c>
+      <c r="F400" s="29">
         <v>15905003</v>
       </c>
-      <c r="G400" s="14">
-        <v>0</v>
-      </c>
-      <c r="H400" s="15">
+      <c r="G400" s="35">
+        <v>0</v>
+      </c>
+      <c r="H400" s="29">
         <v>60</v>
       </c>
-      <c r="I400" s="6">
-        <v>0</v>
-      </c>
-      <c r="J400" s="6">
-        <v>0</v>
-      </c>
-      <c r="K400" s="6">
-        <v>0</v>
-      </c>
-      <c r="L400" s="6">
-        <v>1</v>
-      </c>
-      <c r="M400" s="6">
-        <v>1</v>
-      </c>
-      <c r="N400" s="6">
-        <v>0</v>
-      </c>
-      <c r="O400" s="6">
-        <v>1</v>
-      </c>
-      <c r="P400" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q400" s="6">
-        <v>1</v>
-      </c>
-      <c r="R400" s="6">
-        <v>1</v>
-      </c>
-      <c r="S400" s="6">
-        <v>0</v>
-      </c>
-      <c r="T400" s="6">
-        <v>0</v>
-      </c>
-      <c r="U400" s="6">
-        <v>0</v>
-      </c>
-      <c r="V400" s="6">
-        <v>0</v>
-      </c>
-      <c r="W400" s="6">
-        <v>1</v>
-      </c>
-      <c r="X400" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y400" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z400" s="40" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="401" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C401" s="6">
+      <c r="I400" s="48">
+        <v>0</v>
+      </c>
+      <c r="J400" s="48">
+        <v>0</v>
+      </c>
+      <c r="K400" s="48">
+        <v>0</v>
+      </c>
+      <c r="L400" s="48">
+        <v>1</v>
+      </c>
+      <c r="M400" s="48">
+        <v>1</v>
+      </c>
+      <c r="N400" s="48">
+        <v>0</v>
+      </c>
+      <c r="O400" s="48">
+        <v>1</v>
+      </c>
+      <c r="P400" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q400" s="48">
+        <v>1</v>
+      </c>
+      <c r="R400" s="48">
+        <v>1</v>
+      </c>
+      <c r="S400" s="48">
+        <v>0</v>
+      </c>
+      <c r="T400" s="48">
+        <v>0</v>
+      </c>
+      <c r="U400" s="48">
+        <v>0</v>
+      </c>
+      <c r="V400" s="48">
+        <v>0</v>
+      </c>
+      <c r="W400" s="48">
+        <v>1</v>
+      </c>
+      <c r="X400" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y400" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z400" s="50" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="401" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C401" s="48">
         <v>5004051</v>
       </c>
-      <c r="D401" s="15" t="s">
+      <c r="D401" s="29" t="s">
         <v>557</v>
       </c>
-      <c r="E401" s="6">
-        <v>0</v>
-      </c>
-      <c r="F401" s="15">
+      <c r="E401" s="48">
+        <v>0</v>
+      </c>
+      <c r="F401" s="29">
         <v>15906001</v>
       </c>
-      <c r="G401" s="14">
-        <v>0</v>
-      </c>
-      <c r="H401" s="15">
+      <c r="G401" s="35">
+        <v>0</v>
+      </c>
+      <c r="H401" s="29">
         <v>60</v>
       </c>
-      <c r="I401" s="6">
-        <v>0</v>
-      </c>
-      <c r="J401" s="6">
-        <v>0</v>
-      </c>
-      <c r="K401" s="6">
-        <v>0</v>
-      </c>
-      <c r="L401" s="6">
-        <v>1</v>
-      </c>
-      <c r="M401" s="6">
-        <v>1</v>
-      </c>
-      <c r="N401" s="6">
-        <v>0</v>
-      </c>
-      <c r="O401" s="6">
-        <v>1</v>
-      </c>
-      <c r="P401" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q401" s="6">
-        <v>1</v>
-      </c>
-      <c r="R401" s="6">
-        <v>1</v>
-      </c>
-      <c r="S401" s="6">
-        <v>0</v>
-      </c>
-      <c r="T401" s="6">
-        <v>0</v>
-      </c>
-      <c r="U401" s="6">
-        <v>0</v>
-      </c>
-      <c r="V401" s="6">
-        <v>0</v>
-      </c>
-      <c r="W401" s="6">
-        <v>1</v>
-      </c>
-      <c r="X401" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y401" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z401" s="40" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="402" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C402" s="6">
+      <c r="I401" s="48">
+        <v>0</v>
+      </c>
+      <c r="J401" s="48">
+        <v>0</v>
+      </c>
+      <c r="K401" s="48">
+        <v>0</v>
+      </c>
+      <c r="L401" s="48">
+        <v>1</v>
+      </c>
+      <c r="M401" s="48">
+        <v>1</v>
+      </c>
+      <c r="N401" s="48">
+        <v>0</v>
+      </c>
+      <c r="O401" s="48">
+        <v>1</v>
+      </c>
+      <c r="P401" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q401" s="48">
+        <v>1</v>
+      </c>
+      <c r="R401" s="48">
+        <v>1</v>
+      </c>
+      <c r="S401" s="48">
+        <v>0</v>
+      </c>
+      <c r="T401" s="48">
+        <v>0</v>
+      </c>
+      <c r="U401" s="48">
+        <v>0</v>
+      </c>
+      <c r="V401" s="48">
+        <v>0</v>
+      </c>
+      <c r="W401" s="48">
+        <v>1</v>
+      </c>
+      <c r="X401" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y401" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z401" s="50" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="402" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C402" s="48">
         <v>5004052</v>
       </c>
-      <c r="D402" s="15" t="s">
+      <c r="D402" s="29" t="s">
         <v>559</v>
       </c>
-      <c r="E402" s="6">
-        <v>0</v>
-      </c>
-      <c r="F402" s="15">
+      <c r="E402" s="48">
+        <v>0</v>
+      </c>
+      <c r="F402" s="29">
         <v>15907001</v>
       </c>
-      <c r="G402" s="14">
-        <v>0</v>
-      </c>
-      <c r="H402" s="15">
+      <c r="G402" s="35">
+        <v>0</v>
+      </c>
+      <c r="H402" s="29">
         <v>60</v>
       </c>
-      <c r="I402" s="6">
-        <v>0</v>
-      </c>
-      <c r="J402" s="6">
-        <v>0</v>
-      </c>
-      <c r="K402" s="6">
-        <v>0</v>
-      </c>
-      <c r="L402" s="6">
-        <v>1</v>
-      </c>
-      <c r="M402" s="6">
-        <v>1</v>
-      </c>
-      <c r="N402" s="6">
-        <v>0</v>
-      </c>
-      <c r="O402" s="6">
-        <v>1</v>
-      </c>
-      <c r="P402" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q402" s="6">
-        <v>1</v>
-      </c>
-      <c r="R402" s="6">
-        <v>1</v>
-      </c>
-      <c r="S402" s="6">
-        <v>0</v>
-      </c>
-      <c r="T402" s="6">
-        <v>0</v>
-      </c>
-      <c r="U402" s="6">
-        <v>0</v>
-      </c>
-      <c r="V402" s="6">
-        <v>0</v>
-      </c>
-      <c r="W402" s="6">
-        <v>1</v>
-      </c>
-      <c r="X402" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y402" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z402" s="40" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="403" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C403" s="6">
+      <c r="I402" s="48">
+        <v>0</v>
+      </c>
+      <c r="J402" s="48">
+        <v>0</v>
+      </c>
+      <c r="K402" s="48">
+        <v>0</v>
+      </c>
+      <c r="L402" s="48">
+        <v>1</v>
+      </c>
+      <c r="M402" s="48">
+        <v>1</v>
+      </c>
+      <c r="N402" s="48">
+        <v>0</v>
+      </c>
+      <c r="O402" s="48">
+        <v>1</v>
+      </c>
+      <c r="P402" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q402" s="48">
+        <v>1</v>
+      </c>
+      <c r="R402" s="48">
+        <v>1</v>
+      </c>
+      <c r="S402" s="48">
+        <v>0</v>
+      </c>
+      <c r="T402" s="48">
+        <v>0</v>
+      </c>
+      <c r="U402" s="48">
+        <v>0</v>
+      </c>
+      <c r="V402" s="48">
+        <v>0</v>
+      </c>
+      <c r="W402" s="48">
+        <v>1</v>
+      </c>
+      <c r="X402" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y402" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z402" s="50" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="403" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C403" s="48">
         <v>5004061</v>
       </c>
-      <c r="D403" s="15" t="s">
+      <c r="D403" s="29" t="s">
         <v>560</v>
       </c>
-      <c r="E403" s="6">
-        <v>0</v>
-      </c>
-      <c r="F403" s="15">
+      <c r="E403" s="48">
+        <v>0</v>
+      </c>
+      <c r="F403" s="29">
         <v>15908001</v>
       </c>
-      <c r="G403" s="14">
-        <v>0</v>
-      </c>
-      <c r="H403" s="15">
+      <c r="G403" s="35">
+        <v>0</v>
+      </c>
+      <c r="H403" s="29">
         <v>60</v>
       </c>
-      <c r="I403" s="6">
-        <v>0</v>
-      </c>
-      <c r="J403" s="6">
-        <v>0</v>
-      </c>
-      <c r="K403" s="6">
-        <v>0</v>
-      </c>
-      <c r="L403" s="6">
-        <v>1</v>
-      </c>
-      <c r="M403" s="6">
-        <v>1</v>
-      </c>
-      <c r="N403" s="6">
-        <v>0</v>
-      </c>
-      <c r="O403" s="6">
-        <v>1</v>
-      </c>
-      <c r="P403" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q403" s="6">
-        <v>1</v>
-      </c>
-      <c r="R403" s="6">
-        <v>1</v>
-      </c>
-      <c r="S403" s="6">
-        <v>0</v>
-      </c>
-      <c r="T403" s="6">
-        <v>0</v>
-      </c>
-      <c r="U403" s="6">
-        <v>0</v>
-      </c>
-      <c r="V403" s="6">
-        <v>0</v>
-      </c>
-      <c r="W403" s="6">
-        <v>1</v>
-      </c>
-      <c r="X403" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y403" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z403" s="40" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="404" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C404" s="6">
+      <c r="I403" s="48">
+        <v>0</v>
+      </c>
+      <c r="J403" s="48">
+        <v>0</v>
+      </c>
+      <c r="K403" s="48">
+        <v>0</v>
+      </c>
+      <c r="L403" s="48">
+        <v>1</v>
+      </c>
+      <c r="M403" s="48">
+        <v>1</v>
+      </c>
+      <c r="N403" s="48">
+        <v>0</v>
+      </c>
+      <c r="O403" s="48">
+        <v>1</v>
+      </c>
+      <c r="P403" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q403" s="48">
+        <v>1</v>
+      </c>
+      <c r="R403" s="48">
+        <v>1</v>
+      </c>
+      <c r="S403" s="48">
+        <v>0</v>
+      </c>
+      <c r="T403" s="48">
+        <v>0</v>
+      </c>
+      <c r="U403" s="48">
+        <v>0</v>
+      </c>
+      <c r="V403" s="48">
+        <v>0</v>
+      </c>
+      <c r="W403" s="48">
+        <v>1</v>
+      </c>
+      <c r="X403" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y403" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z403" s="50" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="404" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C404" s="48">
         <v>5004062</v>
       </c>
-      <c r="D404" s="15" t="s">
+      <c r="D404" s="29" t="s">
         <v>561</v>
       </c>
-      <c r="E404" s="6">
-        <v>0</v>
-      </c>
-      <c r="F404" s="15">
+      <c r="E404" s="48">
+        <v>0</v>
+      </c>
+      <c r="F404" s="29">
         <v>15909001</v>
       </c>
-      <c r="G404" s="14">
-        <v>0</v>
-      </c>
-      <c r="H404" s="15">
+      <c r="G404" s="35">
+        <v>0</v>
+      </c>
+      <c r="H404" s="29">
         <v>60</v>
       </c>
-      <c r="I404" s="6">
-        <v>0</v>
-      </c>
-      <c r="J404" s="6">
-        <v>0</v>
-      </c>
-      <c r="K404" s="6">
-        <v>0</v>
-      </c>
-      <c r="L404" s="6">
-        <v>1</v>
-      </c>
-      <c r="M404" s="6">
-        <v>1</v>
-      </c>
-      <c r="N404" s="6">
-        <v>0</v>
-      </c>
-      <c r="O404" s="6">
-        <v>1</v>
-      </c>
-      <c r="P404" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q404" s="6">
-        <v>1</v>
-      </c>
-      <c r="R404" s="6">
-        <v>1</v>
-      </c>
-      <c r="S404" s="6">
-        <v>0</v>
-      </c>
-      <c r="T404" s="6">
-        <v>0</v>
-      </c>
-      <c r="U404" s="6">
-        <v>0</v>
-      </c>
-      <c r="V404" s="6">
-        <v>0</v>
-      </c>
-      <c r="W404" s="6">
-        <v>1</v>
-      </c>
-      <c r="X404" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y404" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z404" s="40" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="405" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C405" s="6">
+      <c r="I404" s="48">
+        <v>0</v>
+      </c>
+      <c r="J404" s="48">
+        <v>0</v>
+      </c>
+      <c r="K404" s="48">
+        <v>0</v>
+      </c>
+      <c r="L404" s="48">
+        <v>1</v>
+      </c>
+      <c r="M404" s="48">
+        <v>1</v>
+      </c>
+      <c r="N404" s="48">
+        <v>0</v>
+      </c>
+      <c r="O404" s="48">
+        <v>1</v>
+      </c>
+      <c r="P404" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q404" s="48">
+        <v>1</v>
+      </c>
+      <c r="R404" s="48">
+        <v>1</v>
+      </c>
+      <c r="S404" s="48">
+        <v>0</v>
+      </c>
+      <c r="T404" s="48">
+        <v>0</v>
+      </c>
+      <c r="U404" s="48">
+        <v>0</v>
+      </c>
+      <c r="V404" s="48">
+        <v>0</v>
+      </c>
+      <c r="W404" s="48">
+        <v>1</v>
+      </c>
+      <c r="X404" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y404" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z404" s="50" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="405" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C405" s="48">
         <v>5004071</v>
       </c>
-      <c r="D405" s="15" t="s">
+      <c r="D405" s="29" t="s">
         <v>562</v>
       </c>
-      <c r="E405" s="6">
-        <v>0</v>
-      </c>
-      <c r="F405" s="15">
+      <c r="E405" s="48">
+        <v>0</v>
+      </c>
+      <c r="F405" s="29">
         <v>15910001</v>
       </c>
-      <c r="G405" s="14">
-        <v>0</v>
-      </c>
-      <c r="H405" s="15">
+      <c r="G405" s="35">
+        <v>0</v>
+      </c>
+      <c r="H405" s="29">
         <v>60</v>
       </c>
-      <c r="I405" s="6">
-        <v>0</v>
-      </c>
-      <c r="J405" s="6">
-        <v>0</v>
-      </c>
-      <c r="K405" s="6">
-        <v>0</v>
-      </c>
-      <c r="L405" s="6">
-        <v>1</v>
-      </c>
-      <c r="M405" s="6">
-        <v>1</v>
-      </c>
-      <c r="N405" s="6">
-        <v>0</v>
-      </c>
-      <c r="O405" s="6">
-        <v>1</v>
-      </c>
-      <c r="P405" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q405" s="6">
-        <v>1</v>
-      </c>
-      <c r="R405" s="6">
-        <v>1</v>
-      </c>
-      <c r="S405" s="6">
-        <v>0</v>
-      </c>
-      <c r="T405" s="6">
-        <v>0</v>
-      </c>
-      <c r="U405" s="6">
-        <v>0</v>
-      </c>
-      <c r="V405" s="6">
-        <v>0</v>
-      </c>
-      <c r="W405" s="6">
-        <v>1</v>
-      </c>
-      <c r="X405" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y405" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z405" s="40" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="406" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C406" s="6">
+      <c r="I405" s="48">
+        <v>0</v>
+      </c>
+      <c r="J405" s="48">
+        <v>0</v>
+      </c>
+      <c r="K405" s="48">
+        <v>0</v>
+      </c>
+      <c r="L405" s="48">
+        <v>1</v>
+      </c>
+      <c r="M405" s="48">
+        <v>1</v>
+      </c>
+      <c r="N405" s="48">
+        <v>0</v>
+      </c>
+      <c r="O405" s="48">
+        <v>1</v>
+      </c>
+      <c r="P405" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q405" s="48">
+        <v>1</v>
+      </c>
+      <c r="R405" s="48">
+        <v>1</v>
+      </c>
+      <c r="S405" s="48">
+        <v>0</v>
+      </c>
+      <c r="T405" s="48">
+        <v>0</v>
+      </c>
+      <c r="U405" s="48">
+        <v>0</v>
+      </c>
+      <c r="V405" s="48">
+        <v>0</v>
+      </c>
+      <c r="W405" s="48">
+        <v>1</v>
+      </c>
+      <c r="X405" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y405" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z405" s="50" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="406" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C406" s="48">
         <v>5004072</v>
       </c>
-      <c r="D406" s="15" t="s">
+      <c r="D406" s="29" t="s">
         <v>564</v>
       </c>
-      <c r="E406" s="6">
-        <v>0</v>
-      </c>
-      <c r="F406" s="15">
+      <c r="E406" s="48">
+        <v>0</v>
+      </c>
+      <c r="F406" s="29">
         <v>15910002</v>
       </c>
-      <c r="G406" s="14">
-        <v>0</v>
-      </c>
-      <c r="H406" s="15">
+      <c r="G406" s="35">
+        <v>0</v>
+      </c>
+      <c r="H406" s="29">
         <v>60</v>
       </c>
-      <c r="I406" s="6">
-        <v>0</v>
-      </c>
-      <c r="J406" s="6">
-        <v>0</v>
-      </c>
-      <c r="K406" s="6">
-        <v>0</v>
-      </c>
-      <c r="L406" s="6">
-        <v>1</v>
-      </c>
-      <c r="M406" s="6">
-        <v>1</v>
-      </c>
-      <c r="N406" s="6">
-        <v>0</v>
-      </c>
-      <c r="O406" s="6">
-        <v>1</v>
-      </c>
-      <c r="P406" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q406" s="6">
-        <v>1</v>
-      </c>
-      <c r="R406" s="6">
-        <v>1</v>
-      </c>
-      <c r="S406" s="6">
-        <v>0</v>
-      </c>
-      <c r="T406" s="6">
-        <v>0</v>
-      </c>
-      <c r="U406" s="6">
-        <v>0</v>
-      </c>
-      <c r="V406" s="6">
-        <v>0</v>
-      </c>
-      <c r="W406" s="6">
-        <v>1</v>
-      </c>
-      <c r="X406" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y406" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z406" s="40" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="407" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C407" s="6">
+      <c r="I406" s="48">
+        <v>0</v>
+      </c>
+      <c r="J406" s="48">
+        <v>0</v>
+      </c>
+      <c r="K406" s="48">
+        <v>0</v>
+      </c>
+      <c r="L406" s="48">
+        <v>1</v>
+      </c>
+      <c r="M406" s="48">
+        <v>1</v>
+      </c>
+      <c r="N406" s="48">
+        <v>0</v>
+      </c>
+      <c r="O406" s="48">
+        <v>1</v>
+      </c>
+      <c r="P406" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q406" s="48">
+        <v>1</v>
+      </c>
+      <c r="R406" s="48">
+        <v>1</v>
+      </c>
+      <c r="S406" s="48">
+        <v>0</v>
+      </c>
+      <c r="T406" s="48">
+        <v>0</v>
+      </c>
+      <c r="U406" s="48">
+        <v>0</v>
+      </c>
+      <c r="V406" s="48">
+        <v>0</v>
+      </c>
+      <c r="W406" s="48">
+        <v>1</v>
+      </c>
+      <c r="X406" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y406" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z406" s="50" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="407" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C407" s="48">
         <v>5004081</v>
       </c>
-      <c r="D407" s="15" t="s">
+      <c r="D407" s="29" t="s">
         <v>565</v>
       </c>
-      <c r="E407" s="6">
-        <v>0</v>
-      </c>
-      <c r="F407" s="15">
+      <c r="E407" s="48">
+        <v>0</v>
+      </c>
+      <c r="F407" s="29">
         <v>15910101</v>
       </c>
-      <c r="G407" s="14">
-        <v>0</v>
-      </c>
-      <c r="H407" s="15">
+      <c r="G407" s="35">
+        <v>0</v>
+      </c>
+      <c r="H407" s="29">
         <v>60</v>
       </c>
-      <c r="I407" s="6">
-        <v>0</v>
-      </c>
-      <c r="J407" s="6">
-        <v>0</v>
-      </c>
-      <c r="K407" s="6">
-        <v>0</v>
-      </c>
-      <c r="L407" s="6">
-        <v>1</v>
-      </c>
-      <c r="M407" s="6">
-        <v>1</v>
-      </c>
-      <c r="N407" s="6">
-        <v>0</v>
-      </c>
-      <c r="O407" s="6">
-        <v>1</v>
-      </c>
-      <c r="P407" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q407" s="6">
-        <v>1</v>
-      </c>
-      <c r="R407" s="6">
-        <v>1</v>
-      </c>
-      <c r="S407" s="6">
-        <v>0</v>
-      </c>
-      <c r="T407" s="6">
-        <v>0</v>
-      </c>
-      <c r="U407" s="6">
-        <v>0</v>
-      </c>
-      <c r="V407" s="6">
-        <v>0</v>
-      </c>
-      <c r="W407" s="6">
-        <v>1</v>
-      </c>
-      <c r="X407" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y407" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z407" s="40" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="408" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C408" s="6">
+      <c r="I407" s="48">
+        <v>0</v>
+      </c>
+      <c r="J407" s="48">
+        <v>0</v>
+      </c>
+      <c r="K407" s="48">
+        <v>0</v>
+      </c>
+      <c r="L407" s="48">
+        <v>1</v>
+      </c>
+      <c r="M407" s="48">
+        <v>1</v>
+      </c>
+      <c r="N407" s="48">
+        <v>0</v>
+      </c>
+      <c r="O407" s="48">
+        <v>1</v>
+      </c>
+      <c r="P407" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q407" s="48">
+        <v>1</v>
+      </c>
+      <c r="R407" s="48">
+        <v>1</v>
+      </c>
+      <c r="S407" s="48">
+        <v>0</v>
+      </c>
+      <c r="T407" s="48">
+        <v>0</v>
+      </c>
+      <c r="U407" s="48">
+        <v>0</v>
+      </c>
+      <c r="V407" s="48">
+        <v>0</v>
+      </c>
+      <c r="W407" s="48">
+        <v>1</v>
+      </c>
+      <c r="X407" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y407" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z407" s="50" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="408" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C408" s="48">
         <v>5004082</v>
       </c>
-      <c r="D408" s="15" t="s">
+      <c r="D408" s="29" t="s">
         <v>566</v>
       </c>
-      <c r="E408" s="6">
-        <v>0</v>
-      </c>
-      <c r="F408" s="15">
+      <c r="E408" s="48">
+        <v>0</v>
+      </c>
+      <c r="F408" s="29">
         <v>15910102</v>
       </c>
-      <c r="G408" s="14">
-        <v>0</v>
-      </c>
-      <c r="H408" s="15">
+      <c r="G408" s="35">
+        <v>0</v>
+      </c>
+      <c r="H408" s="29">
         <v>60</v>
       </c>
-      <c r="I408" s="6">
-        <v>0</v>
-      </c>
-      <c r="J408" s="6">
-        <v>0</v>
-      </c>
-      <c r="K408" s="6">
-        <v>0</v>
-      </c>
-      <c r="L408" s="6">
-        <v>1</v>
-      </c>
-      <c r="M408" s="6">
-        <v>1</v>
-      </c>
-      <c r="N408" s="6">
-        <v>0</v>
-      </c>
-      <c r="O408" s="6">
-        <v>1</v>
-      </c>
-      <c r="P408" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q408" s="6">
-        <v>1</v>
-      </c>
-      <c r="R408" s="6">
-        <v>1</v>
-      </c>
-      <c r="S408" s="6">
-        <v>0</v>
-      </c>
-      <c r="T408" s="6">
-        <v>0</v>
-      </c>
-      <c r="U408" s="6">
-        <v>0</v>
-      </c>
-      <c r="V408" s="6">
-        <v>0</v>
-      </c>
-      <c r="W408" s="6">
-        <v>1</v>
-      </c>
-      <c r="X408" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y408" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z408" s="40" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="409" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C409" s="6">
+      <c r="I408" s="48">
+        <v>0</v>
+      </c>
+      <c r="J408" s="48">
+        <v>0</v>
+      </c>
+      <c r="K408" s="48">
+        <v>0</v>
+      </c>
+      <c r="L408" s="48">
+        <v>1</v>
+      </c>
+      <c r="M408" s="48">
+        <v>1</v>
+      </c>
+      <c r="N408" s="48">
+        <v>0</v>
+      </c>
+      <c r="O408" s="48">
+        <v>1</v>
+      </c>
+      <c r="P408" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q408" s="48">
+        <v>1</v>
+      </c>
+      <c r="R408" s="48">
+        <v>1</v>
+      </c>
+      <c r="S408" s="48">
+        <v>0</v>
+      </c>
+      <c r="T408" s="48">
+        <v>0</v>
+      </c>
+      <c r="U408" s="48">
+        <v>0</v>
+      </c>
+      <c r="V408" s="48">
+        <v>0</v>
+      </c>
+      <c r="W408" s="48">
+        <v>1</v>
+      </c>
+      <c r="X408" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y408" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z408" s="50" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="409" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C409" s="48">
         <v>5004091</v>
       </c>
-      <c r="D409" s="15" t="s">
+      <c r="D409" s="29" t="s">
         <v>567</v>
       </c>
-      <c r="E409" s="6">
-        <v>0</v>
-      </c>
-      <c r="F409" s="15">
+      <c r="E409" s="48">
+        <v>0</v>
+      </c>
+      <c r="F409" s="29">
         <v>15911001</v>
       </c>
-      <c r="G409" s="14">
-        <v>0</v>
-      </c>
-      <c r="H409" s="15">
+      <c r="G409" s="35">
+        <v>0</v>
+      </c>
+      <c r="H409" s="29">
         <v>60</v>
       </c>
-      <c r="I409" s="6">
-        <v>0</v>
-      </c>
-      <c r="J409" s="6">
-        <v>0</v>
-      </c>
-      <c r="K409" s="6">
-        <v>0</v>
-      </c>
-      <c r="L409" s="6">
-        <v>1</v>
-      </c>
-      <c r="M409" s="6">
-        <v>1</v>
-      </c>
-      <c r="N409" s="6">
-        <v>0</v>
-      </c>
-      <c r="O409" s="6">
-        <v>1</v>
-      </c>
-      <c r="P409" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q409" s="6">
-        <v>1</v>
-      </c>
-      <c r="R409" s="6">
-        <v>1</v>
-      </c>
-      <c r="S409" s="6">
-        <v>0</v>
-      </c>
-      <c r="T409" s="6">
-        <v>0</v>
-      </c>
-      <c r="U409" s="6">
-        <v>0</v>
-      </c>
-      <c r="V409" s="6">
-        <v>0</v>
-      </c>
-      <c r="W409" s="6">
-        <v>1</v>
-      </c>
-      <c r="X409" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y409" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z409" s="40" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="410" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C410" s="6">
+      <c r="I409" s="48">
+        <v>0</v>
+      </c>
+      <c r="J409" s="48">
+        <v>0</v>
+      </c>
+      <c r="K409" s="48">
+        <v>0</v>
+      </c>
+      <c r="L409" s="48">
+        <v>1</v>
+      </c>
+      <c r="M409" s="48">
+        <v>1</v>
+      </c>
+      <c r="N409" s="48">
+        <v>0</v>
+      </c>
+      <c r="O409" s="48">
+        <v>1</v>
+      </c>
+      <c r="P409" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q409" s="48">
+        <v>1</v>
+      </c>
+      <c r="R409" s="48">
+        <v>1</v>
+      </c>
+      <c r="S409" s="48">
+        <v>0</v>
+      </c>
+      <c r="T409" s="48">
+        <v>0</v>
+      </c>
+      <c r="U409" s="48">
+        <v>0</v>
+      </c>
+      <c r="V409" s="48">
+        <v>0</v>
+      </c>
+      <c r="W409" s="48">
+        <v>1</v>
+      </c>
+      <c r="X409" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y409" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z409" s="50" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="410" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C410" s="48">
         <v>5004092</v>
       </c>
-      <c r="D410" s="15" t="s">
+      <c r="D410" s="29" t="s">
         <v>569</v>
       </c>
-      <c r="E410" s="6">
-        <v>0</v>
-      </c>
-      <c r="F410" s="15">
+      <c r="E410" s="48">
+        <v>0</v>
+      </c>
+      <c r="F410" s="29">
         <v>15911002</v>
       </c>
-      <c r="G410" s="14">
-        <v>0</v>
-      </c>
-      <c r="H410" s="15">
+      <c r="G410" s="35">
+        <v>0</v>
+      </c>
+      <c r="H410" s="29">
         <v>60</v>
       </c>
-      <c r="I410" s="6">
-        <v>0</v>
-      </c>
-      <c r="J410" s="6">
-        <v>0</v>
-      </c>
-      <c r="K410" s="6">
-        <v>0</v>
-      </c>
-      <c r="L410" s="6">
-        <v>1</v>
-      </c>
-      <c r="M410" s="6">
-        <v>1</v>
-      </c>
-      <c r="N410" s="6">
-        <v>0</v>
-      </c>
-      <c r="O410" s="6">
-        <v>1</v>
-      </c>
-      <c r="P410" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q410" s="6">
-        <v>1</v>
-      </c>
-      <c r="R410" s="6">
-        <v>1</v>
-      </c>
-      <c r="S410" s="6">
-        <v>0</v>
-      </c>
-      <c r="T410" s="6">
-        <v>0</v>
-      </c>
-      <c r="U410" s="6">
-        <v>0</v>
-      </c>
-      <c r="V410" s="6">
-        <v>0</v>
-      </c>
-      <c r="W410" s="6">
-        <v>1</v>
-      </c>
-      <c r="X410" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y410" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z410" s="40" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="411" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C411" s="6">
+      <c r="I410" s="48">
+        <v>0</v>
+      </c>
+      <c r="J410" s="48">
+        <v>0</v>
+      </c>
+      <c r="K410" s="48">
+        <v>0</v>
+      </c>
+      <c r="L410" s="48">
+        <v>1</v>
+      </c>
+      <c r="M410" s="48">
+        <v>1</v>
+      </c>
+      <c r="N410" s="48">
+        <v>0</v>
+      </c>
+      <c r="O410" s="48">
+        <v>1</v>
+      </c>
+      <c r="P410" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q410" s="48">
+        <v>1</v>
+      </c>
+      <c r="R410" s="48">
+        <v>1</v>
+      </c>
+      <c r="S410" s="48">
+        <v>0</v>
+      </c>
+      <c r="T410" s="48">
+        <v>0</v>
+      </c>
+      <c r="U410" s="48">
+        <v>0</v>
+      </c>
+      <c r="V410" s="48">
+        <v>0</v>
+      </c>
+      <c r="W410" s="48">
+        <v>1</v>
+      </c>
+      <c r="X410" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y410" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z410" s="50" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="411" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C411" s="48">
         <v>5004093</v>
       </c>
-      <c r="D411" s="15" t="s">
+      <c r="D411" s="29" t="s">
         <v>570</v>
       </c>
-      <c r="E411" s="6">
-        <v>0</v>
-      </c>
-      <c r="F411" s="15">
+      <c r="E411" s="48">
+        <v>0</v>
+      </c>
+      <c r="F411" s="29">
         <v>15911003</v>
       </c>
-      <c r="G411" s="14">
-        <v>0</v>
-      </c>
-      <c r="H411" s="15">
+      <c r="G411" s="35">
+        <v>0</v>
+      </c>
+      <c r="H411" s="29">
         <v>60</v>
       </c>
-      <c r="I411" s="6">
-        <v>0</v>
-      </c>
-      <c r="J411" s="6">
-        <v>0</v>
-      </c>
-      <c r="K411" s="6">
-        <v>0</v>
-      </c>
-      <c r="L411" s="6">
-        <v>1</v>
-      </c>
-      <c r="M411" s="6">
-        <v>1</v>
-      </c>
-      <c r="N411" s="6">
-        <v>0</v>
-      </c>
-      <c r="O411" s="6">
-        <v>1</v>
-      </c>
-      <c r="P411" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q411" s="6">
-        <v>1</v>
-      </c>
-      <c r="R411" s="6">
-        <v>1</v>
-      </c>
-      <c r="S411" s="6">
-        <v>0</v>
-      </c>
-      <c r="T411" s="6">
-        <v>0</v>
-      </c>
-      <c r="U411" s="6">
-        <v>0</v>
-      </c>
-      <c r="V411" s="6">
-        <v>0</v>
-      </c>
-      <c r="W411" s="6">
-        <v>1</v>
-      </c>
-      <c r="X411" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y411" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z411" s="40" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="412" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C412" s="6">
+      <c r="I411" s="48">
+        <v>0</v>
+      </c>
+      <c r="J411" s="48">
+        <v>0</v>
+      </c>
+      <c r="K411" s="48">
+        <v>0</v>
+      </c>
+      <c r="L411" s="48">
+        <v>1</v>
+      </c>
+      <c r="M411" s="48">
+        <v>1</v>
+      </c>
+      <c r="N411" s="48">
+        <v>0</v>
+      </c>
+      <c r="O411" s="48">
+        <v>1</v>
+      </c>
+      <c r="P411" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q411" s="48">
+        <v>1</v>
+      </c>
+      <c r="R411" s="48">
+        <v>1</v>
+      </c>
+      <c r="S411" s="48">
+        <v>0</v>
+      </c>
+      <c r="T411" s="48">
+        <v>0</v>
+      </c>
+      <c r="U411" s="48">
+        <v>0</v>
+      </c>
+      <c r="V411" s="48">
+        <v>0</v>
+      </c>
+      <c r="W411" s="48">
+        <v>1</v>
+      </c>
+      <c r="X411" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y411" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z411" s="50" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="412" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C412" s="48">
         <v>5004101</v>
       </c>
-      <c r="D412" s="15" t="s">
+      <c r="D412" s="29" t="s">
         <v>606</v>
       </c>
-      <c r="E412" s="6">
-        <v>0</v>
-      </c>
-      <c r="F412" s="15">
+      <c r="E412" s="48">
+        <v>0</v>
+      </c>
+      <c r="F412" s="29">
         <v>15910201</v>
       </c>
-      <c r="G412" s="14">
-        <v>0</v>
-      </c>
-      <c r="H412" s="15">
+      <c r="G412" s="35">
+        <v>0</v>
+      </c>
+      <c r="H412" s="29">
         <v>60</v>
       </c>
-      <c r="I412" s="6">
-        <v>0</v>
-      </c>
-      <c r="J412" s="6">
-        <v>0</v>
-      </c>
-      <c r="K412" s="6">
-        <v>0</v>
-      </c>
-      <c r="L412" s="6">
-        <v>1</v>
-      </c>
-      <c r="M412" s="6">
-        <v>1</v>
-      </c>
-      <c r="N412" s="6">
-        <v>0</v>
-      </c>
-      <c r="O412" s="6">
-        <v>1</v>
-      </c>
-      <c r="P412" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q412" s="6">
-        <v>1</v>
-      </c>
-      <c r="R412" s="6">
-        <v>1</v>
-      </c>
-      <c r="S412" s="6">
-        <v>0</v>
-      </c>
-      <c r="T412" s="6">
-        <v>0</v>
-      </c>
-      <c r="U412" s="6">
-        <v>0</v>
-      </c>
-      <c r="V412" s="6">
-        <v>0</v>
-      </c>
-      <c r="W412" s="6">
-        <v>1</v>
-      </c>
-      <c r="X412" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y412" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z412" s="40" t="s">
-        <v>634</v>
+      <c r="I412" s="48">
+        <v>0</v>
+      </c>
+      <c r="J412" s="48">
+        <v>0</v>
+      </c>
+      <c r="K412" s="48">
+        <v>0</v>
+      </c>
+      <c r="L412" s="48">
+        <v>1</v>
+      </c>
+      <c r="M412" s="48">
+        <v>1</v>
+      </c>
+      <c r="N412" s="48">
+        <v>0</v>
+      </c>
+      <c r="O412" s="48">
+        <v>1</v>
+      </c>
+      <c r="P412" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q412" s="48">
+        <v>1</v>
+      </c>
+      <c r="R412" s="48">
+        <v>1</v>
+      </c>
+      <c r="S412" s="48">
+        <v>0</v>
+      </c>
+      <c r="T412" s="48">
+        <v>0</v>
+      </c>
+      <c r="U412" s="48">
+        <v>0</v>
+      </c>
+      <c r="V412" s="48">
+        <v>0</v>
+      </c>
+      <c r="W412" s="48">
+        <v>1</v>
+      </c>
+      <c r="X412" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y412" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z412" s="50" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="413" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">

--- a/Excel/EquipMakeConfig.xlsx
+++ b/Excel/EquipMakeConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1502CA66-DD7C-4C66-AD64-B6F1319C34BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5522B70F-0E6C-4F53-BD14-88A3C56D9A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32514,7 +32514,7 @@
         <v>0</v>
       </c>
       <c r="H386" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I386" s="48">
         <v>0</v>
@@ -32588,7 +32588,7 @@
         <v>0</v>
       </c>
       <c r="H387" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I387" s="48">
         <v>0</v>
@@ -32662,7 +32662,7 @@
         <v>0</v>
       </c>
       <c r="H388" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I388" s="48">
         <v>0</v>
@@ -32736,7 +32736,7 @@
         <v>0</v>
       </c>
       <c r="H389" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I389" s="48">
         <v>0</v>
@@ -32810,7 +32810,7 @@
         <v>0</v>
       </c>
       <c r="H390" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I390" s="48">
         <v>0</v>
@@ -32884,7 +32884,7 @@
         <v>0</v>
       </c>
       <c r="H391" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I391" s="48">
         <v>0</v>
@@ -32958,7 +32958,7 @@
         <v>0</v>
       </c>
       <c r="H392" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I392" s="48">
         <v>0</v>
@@ -33032,7 +33032,7 @@
         <v>0</v>
       </c>
       <c r="H393" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I393" s="48">
         <v>0</v>
@@ -33106,7 +33106,7 @@
         <v>0</v>
       </c>
       <c r="H394" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I394" s="48">
         <v>0</v>
@@ -33180,7 +33180,7 @@
         <v>0</v>
       </c>
       <c r="H395" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I395" s="48">
         <v>0</v>
@@ -33254,7 +33254,7 @@
         <v>0</v>
       </c>
       <c r="H396" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I396" s="48">
         <v>0</v>
@@ -33328,7 +33328,7 @@
         <v>0</v>
       </c>
       <c r="H397" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I397" s="48">
         <v>0</v>
@@ -33402,7 +33402,7 @@
         <v>0</v>
       </c>
       <c r="H398" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I398" s="48">
         <v>0</v>
@@ -33476,7 +33476,7 @@
         <v>0</v>
       </c>
       <c r="H399" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I399" s="48">
         <v>0</v>
@@ -33550,7 +33550,7 @@
         <v>0</v>
       </c>
       <c r="H400" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I400" s="48">
         <v>0</v>
@@ -33624,7 +33624,7 @@
         <v>0</v>
       </c>
       <c r="H401" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I401" s="48">
         <v>0</v>
@@ -33698,7 +33698,7 @@
         <v>0</v>
       </c>
       <c r="H402" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I402" s="48">
         <v>0</v>
@@ -33772,7 +33772,7 @@
         <v>0</v>
       </c>
       <c r="H403" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I403" s="48">
         <v>0</v>
@@ -33846,7 +33846,7 @@
         <v>0</v>
       </c>
       <c r="H404" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I404" s="48">
         <v>0</v>
@@ -33920,7 +33920,7 @@
         <v>0</v>
       </c>
       <c r="H405" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I405" s="48">
         <v>0</v>
@@ -33994,7 +33994,7 @@
         <v>0</v>
       </c>
       <c r="H406" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I406" s="48">
         <v>0</v>
@@ -34068,7 +34068,7 @@
         <v>0</v>
       </c>
       <c r="H407" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I407" s="48">
         <v>0</v>
@@ -34142,7 +34142,7 @@
         <v>0</v>
       </c>
       <c r="H408" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I408" s="48">
         <v>0</v>
@@ -34216,7 +34216,7 @@
         <v>0</v>
       </c>
       <c r="H409" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I409" s="48">
         <v>0</v>
@@ -34290,7 +34290,7 @@
         <v>0</v>
       </c>
       <c r="H410" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I410" s="48">
         <v>0</v>
@@ -34364,7 +34364,7 @@
         <v>0</v>
       </c>
       <c r="H411" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I411" s="48">
         <v>0</v>
@@ -34438,7 +34438,7 @@
         <v>0</v>
       </c>
       <c r="H412" s="29">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I412" s="48">
         <v>0</v>

--- a/Excel/EquipMakeConfig.xlsx
+++ b/Excel/EquipMakeConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5522B70F-0E6C-4F53-BD14-88A3C56D9A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA458DB-11A7-4CE1-954D-CB2928416E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipMakeProto" sheetId="1" r:id="rId1"/>
@@ -3171,82 +3171,82 @@
     <t>10033008;1@10033008;1@10033010;1</t>
   </si>
   <si>
-    <t>10000165;30@10000182;30@15801001;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15801002;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15801003;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15802001;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15802002;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15802003;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15803001;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15803002;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15803003;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15804001;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15804002;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15804003;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15805001;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15805002;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;30@10000182;30@15805003;1@10010085;10000@10000152;50@10000143;50</t>
-  </si>
-  <si>
-    <t>10000165;40@10000182;40@15806001;1@10010085;10000@10000152;75@10000143;75</t>
-  </si>
-  <si>
-    <t>10000165;40@10000182;40@15807001;1@10010085;10000@10000152;75@10000143;75</t>
-  </si>
-  <si>
-    <t>10000165;40@10000182;40@15808001;1@10010085;10000@10000152;75@10000143;75</t>
-  </si>
-  <si>
-    <t>10000165;40@10000182;40@15809001;1@10010085;10000@10000152;75@10000143;75</t>
-  </si>
-  <si>
-    <t>10000165;80@10000182;80@15810001;1@10010085;10000@10000152;150@10000143;150</t>
-  </si>
-  <si>
-    <t>10000165;80@10000182;80@15810002;1@10010085;10000@10000152;150@10000143;150</t>
-  </si>
-  <si>
-    <t>10000165;80@10000182;80@15810101;1@10010085;10000@10000152;150@10000143;150</t>
-  </si>
-  <si>
-    <t>10000165;80@10000182;80@15810102;1@10010085;10000@10000152;150@10000143;150</t>
-  </si>
-  <si>
-    <t>10000165;60@10000182;60@15811001;1@10010085;10000@10000152;100@10000143;100</t>
-  </si>
-  <si>
-    <t>10000165;60@10000182;60@15811002;1@10010085;10000@10000152;100@10000143;100</t>
-  </si>
-  <si>
-    <t>10000165;60@10000182;60@15811003;1@10010085;10000@10000152;100@10000143;100</t>
+    <t>10000165;80@10000182;100@15810001;1@10010085;10000@10000152;150@10000143;150</t>
+  </si>
+  <si>
+    <t>10000165;80@10000182;100@15810002;1@10010085;10000@10000152;150@10000143;150</t>
+  </si>
+  <si>
+    <t>10000165;80@10000182;100@15810101;1@10010085;10000@10000152;150@10000143;150</t>
+  </si>
+  <si>
+    <t>10000165;80@10000182;100@15810102;1@10010085;10000@10000152;150@10000143;150</t>
+  </si>
+  <si>
+    <t>10000165;60@10000182;80@15811001;1@10010085;10000@10000152;100@10000143;100</t>
+  </si>
+  <si>
+    <t>10000165;60@10000182;80@15811002;1@10010085;10000@10000152;100@10000143;100</t>
+  </si>
+  <si>
+    <t>10000165;60@10000182;80@15811003;1@10010085;10000@10000152;100@10000143;100</t>
+  </si>
+  <si>
+    <t>10000165;40@10000182;60@15806001;1@10010085;10000@10000152;75@10000143;75</t>
+  </si>
+  <si>
+    <t>10000165;40@10000182;60@15807001;1@10010085;10000@10000152;75@10000143;75</t>
+  </si>
+  <si>
+    <t>10000165;40@10000182;60@15808001;1@10010085;10000@10000152;75@10000143;75</t>
+  </si>
+  <si>
+    <t>10000165;40@10000182;60@15809001;1@10010085;10000@10000152;75@10000143;75</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15801001;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15801002;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15801003;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15802001;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15802002;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15802003;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15803001;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15803002;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15803003;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15804001;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15804002;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15804003;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15805001;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15805002;1@10010085;10000@10000152;50@10000143;50</t>
+  </si>
+  <si>
+    <t>10000165;30@10000182;40@15805003;1@10010085;10000@10000152;50@10000143;50</t>
   </si>
 </sst>
 </file>
@@ -32568,7 +32568,7 @@
         <v>0</v>
       </c>
       <c r="Z386" s="50" t="s">
-        <v>875</v>
+        <v>886</v>
       </c>
     </row>
     <row r="387" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -32642,7 +32642,7 @@
         <v>0</v>
       </c>
       <c r="Z387" s="50" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
     </row>
     <row r="388" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -32716,7 +32716,7 @@
         <v>0</v>
       </c>
       <c r="Z388" s="50" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
     </row>
     <row r="389" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -32790,7 +32790,7 @@
         <v>0</v>
       </c>
       <c r="Z389" s="50" t="s">
-        <v>878</v>
+        <v>889</v>
       </c>
     </row>
     <row r="390" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -32864,7 +32864,7 @@
         <v>0</v>
       </c>
       <c r="Z390" s="50" t="s">
-        <v>879</v>
+        <v>890</v>
       </c>
     </row>
     <row r="391" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -32938,7 +32938,7 @@
         <v>0</v>
       </c>
       <c r="Z391" s="50" t="s">
-        <v>880</v>
+        <v>891</v>
       </c>
     </row>
     <row r="392" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33012,7 +33012,7 @@
         <v>0</v>
       </c>
       <c r="Z392" s="50" t="s">
-        <v>881</v>
+        <v>892</v>
       </c>
     </row>
     <row r="393" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33086,7 +33086,7 @@
         <v>0</v>
       </c>
       <c r="Z393" s="50" t="s">
-        <v>882</v>
+        <v>893</v>
       </c>
     </row>
     <row r="394" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33160,7 +33160,7 @@
         <v>0</v>
       </c>
       <c r="Z394" s="50" t="s">
-        <v>883</v>
+        <v>894</v>
       </c>
     </row>
     <row r="395" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33234,7 +33234,7 @@
         <v>0</v>
       </c>
       <c r="Z395" s="50" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
     </row>
     <row r="396" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33308,7 +33308,7 @@
         <v>0</v>
       </c>
       <c r="Z396" s="50" t="s">
-        <v>885</v>
+        <v>896</v>
       </c>
     </row>
     <row r="397" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33382,7 +33382,7 @@
         <v>0</v>
       </c>
       <c r="Z397" s="50" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
     </row>
     <row r="398" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33456,7 +33456,7 @@
         <v>0</v>
       </c>
       <c r="Z398" s="50" t="s">
-        <v>887</v>
+        <v>898</v>
       </c>
     </row>
     <row r="399" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33530,7 +33530,7 @@
         <v>0</v>
       </c>
       <c r="Z399" s="50" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
     </row>
     <row r="400" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33604,7 +33604,7 @@
         <v>0</v>
       </c>
       <c r="Z400" s="50" t="s">
-        <v>889</v>
+        <v>900</v>
       </c>
     </row>
     <row r="401" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33678,7 +33678,7 @@
         <v>0</v>
       </c>
       <c r="Z401" s="50" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
     </row>
     <row r="402" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33752,7 +33752,7 @@
         <v>0</v>
       </c>
       <c r="Z402" s="50" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
     </row>
     <row r="403" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33826,7 +33826,7 @@
         <v>0</v>
       </c>
       <c r="Z403" s="50" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
     </row>
     <row r="404" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33900,7 +33900,7 @@
         <v>0</v>
       </c>
       <c r="Z404" s="50" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
     </row>
     <row r="405" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -33974,7 +33974,7 @@
         <v>0</v>
       </c>
       <c r="Z405" s="50" t="s">
-        <v>894</v>
+        <v>875</v>
       </c>
     </row>
     <row r="406" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -34048,7 +34048,7 @@
         <v>0</v>
       </c>
       <c r="Z406" s="50" t="s">
-        <v>895</v>
+        <v>876</v>
       </c>
     </row>
     <row r="407" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -34122,7 +34122,7 @@
         <v>0</v>
       </c>
       <c r="Z407" s="50" t="s">
-        <v>896</v>
+        <v>877</v>
       </c>
     </row>
     <row r="408" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -34196,7 +34196,7 @@
         <v>0</v>
       </c>
       <c r="Z408" s="50" t="s">
-        <v>897</v>
+        <v>878</v>
       </c>
     </row>
     <row r="409" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -34270,7 +34270,7 @@
         <v>0</v>
       </c>
       <c r="Z409" s="50" t="s">
-        <v>898</v>
+        <v>879</v>
       </c>
     </row>
     <row r="410" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -34344,7 +34344,7 @@
         <v>0</v>
       </c>
       <c r="Z410" s="50" t="s">
-        <v>899</v>
+        <v>880</v>
       </c>
     </row>
     <row r="411" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -34418,7 +34418,7 @@
         <v>0</v>
       </c>
       <c r="Z411" s="50" t="s">
-        <v>900</v>
+        <v>881</v>
       </c>
     </row>
     <row r="412" spans="3:26" s="48" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -34492,7 +34492,7 @@
         <v>0</v>
       </c>
       <c r="Z412" s="50" t="s">
-        <v>897</v>
+        <v>878</v>
       </c>
     </row>
     <row r="413" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">

--- a/Excel/EquipMakeConfig.xlsx
+++ b/Excel/EquipMakeConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0AE0C74-E466-4491-A5DB-EF4686929B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E1C530-9DBD-4BA5-B244-457437E49B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipMakeProto" sheetId="1" r:id="rId1"/>
@@ -477,7 +477,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="904">
   <si>
     <t>#</t>
   </si>
@@ -3254,6 +3254,10 @@
   </si>
   <si>
     <t>10010033;3</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000165;80@10000182;100@15810201;1@10010085;10000@10000152;150@10000143;150</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -34574,7 +34578,7 @@
         <v>0</v>
       </c>
       <c r="Z413" s="50" t="s">
-        <v>878</v>
+        <v>903</v>
       </c>
     </row>
     <row r="414" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">

--- a/Excel/EquipMakeConfig.xlsx
+++ b/Excel/EquipMakeConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A52973-5FAF-42BF-BAD6-B97A3CD810D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566C8BFD-D8AC-49D2-BE37-A25053D7068E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3335,15 +3335,15 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>10000169;10@10000166;120@10000143;50@10000168;100@10010086;30@11500501;1</t>
+    <t>10000169;10@10000166;100@10000143;50@10000168;100@10010086;30@11500501;1</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>10000169;10@10000166;120@10000143;50@10000168;100@10010086;30@11500503;1</t>
+    <t>10000169;10@10000166;100@10000143;50@10000168;100@10010086;30@11500502;1</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>10000169;10@10000166;120@10000143;50@10000168;100@10010086;30@11500502;1</t>
+    <t>10000169;10@10000166;100@10000143;50@10000168;100@10010086;30@11500503;1</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -36662,7 +36662,7 @@
         <v>0</v>
       </c>
       <c r="Z440" s="40" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="441" spans="3:26" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -36736,7 +36736,7 @@
         <v>0</v>
       </c>
       <c r="Z441" s="40" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="442" spans="3:26" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
